--- a/www/flightdata/xlsx/eoss-335.xlsx
+++ b/www/flightdata/xlsx/eoss-335.xlsx
@@ -3126,7 +3126,7 @@
         <v>31589.17</v>
       </c>
       <c r="I2">
-        <v>525</v>
+        <v>384</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
